--- a/Solutions/Assignment 1.xlsx
+++ b/Solutions/Assignment 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\دوره جامع تحلیل گر داده\1 -Excel\ارسالی\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\دوره جامع تحلیل گر داده\1 -Excel\جواب\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685B5567-2F16-4398-B622-D63AE3BB6FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFAE8EC-0968-4D14-844A-21BB82C2D2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="30">
   <si>
     <t>age</t>
   </si>
@@ -133,13 +133,16 @@
     <t>High</t>
   </si>
   <si>
-    <t>south</t>
-  </si>
-  <si>
     <t>east</t>
   </si>
   <si>
     <t>در این تمرین، با استفاده از لیست‌های طراحی‌شده، امکان مشاهده و انتخاب مقادیر موردنظر فراهم شده است.</t>
+  </si>
+  <si>
+    <t>north</t>
+  </si>
+  <si>
+    <t>Average BWI</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1077,7 @@
   <cols>
     <col min="4" max="4" width="9.6640625" customWidth="1"/>
     <col min="5" max="5" width="9.109375" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.77734375" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" customWidth="1"/>
     <col min="10" max="10" width="13.33203125" customWidth="1"/>
@@ -1187,7 +1190,7 @@
         <v>High</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -1274,7 +1277,7 @@
         <v>17</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
@@ -1316,19 +1319,19 @@
         <v>Medium</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M6" s="2">
         <f>COUNTIF(Medical[North_South],L6)</f>
-        <v>689</v>
+        <v>649</v>
       </c>
       <c r="N6" s="2">
         <f>SUMIF(Medical[North_South],L6,G:G)</f>
-        <v>8734119.4645499978</v>
+        <v>8992564.1659089997</v>
       </c>
       <c r="O6" s="2">
-        <f>AVERAGEIF(Medical[North_South],L6,Medical[charges])</f>
-        <v>13608.772729912916</v>
+        <f>AVERAGEIF(Medical[North_South],L6,Medical[bmi])</f>
+        <v>29.186664098613257</v>
       </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
@@ -1370,7 +1373,7 @@
         <v>Medium</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M7" s="2">
         <f>COUNTIF(Medical[East_West],L7)</f>
@@ -1381,8 +1384,8 @@
         <v>9707358.346598994</v>
       </c>
       <c r="O7" s="2">
-        <f>AVERAGEIF(Medical[East_West],L7,Medical[charges])</f>
-        <v>14109.532480521793</v>
+        <f>AVERAGEIF(Medical[East_West],L7,Medical[bmi])</f>
+        <v>31.386329941860485</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
